--- a/01_proyecto/trim3/02_normalizacion/normalizacion.xlsx
+++ b/01_proyecto/trim3/02_normalizacion/normalizacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZUS\Desktop\manuales\manual tecnico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D308AA0A-EA7B-4E42-BA80-82C55A66E12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41038432-020D-490A-96BC-D82DC94677FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{607F096B-C565-4516-AFC9-EBB8442A0C72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{607F096B-C565-4516-AFC9-EBB8442A0C72}"/>
   </bookViews>
   <sheets>
     <sheet name="1FN" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="370">
   <si>
     <t>Usuario</t>
   </si>
@@ -851,13 +851,310 @@
   </si>
   <si>
     <t>grnade</t>
+  </si>
+  <si>
+    <t>Imagen</t>
+  </si>
+  <si>
+    <t>idImagen</t>
+  </si>
+  <si>
+    <t>urlImagen</t>
+  </si>
+  <si>
+    <t>img/foto1</t>
+  </si>
+  <si>
+    <t>img/foto2</t>
+  </si>
+  <si>
+    <t>img/foto3</t>
+  </si>
+  <si>
+    <t>img/foto4</t>
+  </si>
+  <si>
+    <t>img/foto5</t>
+  </si>
+  <si>
+    <t>img/foto6</t>
+  </si>
+  <si>
+    <t>img/foto7</t>
+  </si>
+  <si>
+    <t>img/foto8</t>
+  </si>
+  <si>
+    <t>img/foto9</t>
+  </si>
+  <si>
+    <t>img/foto10</t>
+  </si>
+  <si>
+    <t>imagen</t>
+  </si>
+  <si>
+    <t>banner</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>titulo</t>
+  </si>
+  <si>
+    <t>file_name</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>fecha_creacion</t>
+  </si>
+  <si>
+    <t>banner1</t>
+  </si>
+  <si>
+    <t>banner2</t>
+  </si>
+  <si>
+    <t>banner3</t>
+  </si>
+  <si>
+    <t>banner4</t>
+  </si>
+  <si>
+    <t>banner5</t>
+  </si>
+  <si>
+    <t>banner6</t>
+  </si>
+  <si>
+    <t>banner7</t>
+  </si>
+  <si>
+    <t>banner8</t>
+  </si>
+  <si>
+    <t>banner9</t>
+  </si>
+  <si>
+    <t>es el banner 1</t>
+  </si>
+  <si>
+    <t>es el banner 2</t>
+  </si>
+  <si>
+    <t>es el banner 3</t>
+  </si>
+  <si>
+    <t>es el banner 4</t>
+  </si>
+  <si>
+    <t>es el banner 5</t>
+  </si>
+  <si>
+    <t>es el banner 6</t>
+  </si>
+  <si>
+    <t>es el banner 7</t>
+  </si>
+  <si>
+    <t>es el banner 8</t>
+  </si>
+  <si>
+    <t>es el banner 9</t>
+  </si>
+  <si>
+    <t>banner1.png</t>
+  </si>
+  <si>
+    <t>banner2.png</t>
+  </si>
+  <si>
+    <t>banner3.png</t>
+  </si>
+  <si>
+    <t>banner4.png</t>
+  </si>
+  <si>
+    <t>banner5.png</t>
+  </si>
+  <si>
+    <t>banner6.png</t>
+  </si>
+  <si>
+    <t>banner7.png</t>
+  </si>
+  <si>
+    <t>banner8.png</t>
+  </si>
+  <si>
+    <t>banner9.png</t>
+  </si>
+  <si>
+    <t>img/banner1</t>
+  </si>
+  <si>
+    <t>img/banner2</t>
+  </si>
+  <si>
+    <t>img/banner3</t>
+  </si>
+  <si>
+    <t>img/banner4</t>
+  </si>
+  <si>
+    <t>img/banner5</t>
+  </si>
+  <si>
+    <t>img/banner6</t>
+  </si>
+  <si>
+    <t>img/banner7</t>
+  </si>
+  <si>
+    <t>img/banner8</t>
+  </si>
+  <si>
+    <t>img/banner9</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>mensajes</t>
+  </si>
+  <si>
+    <t>usuario</t>
+  </si>
+  <si>
+    <t>contenido</t>
+  </si>
+  <si>
+    <t>respuesta</t>
+  </si>
+  <si>
+    <t>fecha_respuesta</t>
+  </si>
+  <si>
+    <t>Lamentamos los incovenientes</t>
+  </si>
+  <si>
+    <t>gracias por su compra</t>
+  </si>
+  <si>
+    <t>Lamentamos los incovenientes, lo solucionaremos</t>
+  </si>
+  <si>
+    <t>SUGERENCIA</t>
+  </si>
+  <si>
+    <t>RECLAMO</t>
+  </si>
+  <si>
+    <t>SolicitudPago</t>
+  </si>
+  <si>
+    <t>idSolicitudPago</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>Pago de compra</t>
+  </si>
+  <si>
+    <t>RespuestaPago</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>clientSecret</t>
+  </si>
+  <si>
+    <t>pagado</t>
+  </si>
+  <si>
+    <t>2dr3f22</t>
+  </si>
+  <si>
+    <t>fef232</t>
+  </si>
+  <si>
+    <t>eff3fe3</t>
+  </si>
+  <si>
+    <t>f3ef3f3e</t>
+  </si>
+  <si>
+    <t>g45343</t>
+  </si>
+  <si>
+    <t>DetallesComprobanteDeVenta</t>
+  </si>
+  <si>
+    <t>idDetallesComprobanteDeVenta</t>
+  </si>
+  <si>
+    <t>idComprobanteDeVenta</t>
+  </si>
+  <si>
+    <t>precio_unitario</t>
+  </si>
+  <si>
+    <t>devoluciones_Cambios</t>
+  </si>
+  <si>
+    <t>id_devolucion</t>
+  </si>
+  <si>
+    <t>motivo</t>
+  </si>
+  <si>
+    <t>tipo_solicitud</t>
+  </si>
+  <si>
+    <t>estado_solicitud</t>
+  </si>
+  <si>
+    <t>fecha_solicitud</t>
+  </si>
+  <si>
+    <t>no me gusto</t>
+  </si>
+  <si>
+    <t>muy grande</t>
+  </si>
+  <si>
+    <t>no era el color</t>
+  </si>
+  <si>
+    <t>cambio</t>
+  </si>
+  <si>
+    <t>denegada</t>
+  </si>
+  <si>
+    <t>en proceso</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -884,6 +1181,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -972,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -997,9 +1300,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,9 +1308,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,6 +1318,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,20 +1682,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -1810,22 +2116,22 @@
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
@@ -2312,26 +2618,26 @@
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-      <c r="K30" s="13" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="14"/>
+      <c r="K30" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="15"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="14"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -2884,17 +3190,17 @@
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
@@ -3254,20 +3560,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="15"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -3688,21 +3994,22 @@
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="15"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
@@ -3744,6 +4051,9 @@
       <c r="N19" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="O19" s="20" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="20" spans="2:15" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
@@ -3785,6 +4095,9 @@
       <c r="N20" s="1">
         <v>1</v>
       </c>
+      <c r="O20" s="1" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="21" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
@@ -3826,6 +4139,9 @@
       <c r="N21" s="1">
         <v>2</v>
       </c>
+      <c r="O21" s="1" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="22" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
@@ -3867,6 +4183,9 @@
       <c r="N22" s="1">
         <v>3</v>
       </c>
+      <c r="O22" s="1" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="23" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
@@ -3907,6 +4226,9 @@
       </c>
       <c r="N23" s="1">
         <v>4</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="2:15" ht="30" x14ac:dyDescent="0.25">
@@ -3949,6 +4271,9 @@
       <c r="N24" s="1">
         <v>5</v>
       </c>
+      <c r="O24" s="1" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
@@ -3990,6 +4315,9 @@
       <c r="N25" s="1">
         <v>1</v>
       </c>
+      <c r="O25" s="1" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="26" spans="2:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
@@ -4031,6 +4359,9 @@
       <c r="N26" s="1">
         <v>2</v>
       </c>
+      <c r="O26" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="27" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
@@ -4072,6 +4403,9 @@
       <c r="N27" s="1">
         <v>3</v>
       </c>
+      <c r="O27" s="1" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
@@ -4113,6 +4447,9 @@
       <c r="N28" s="1">
         <v>4</v>
       </c>
+      <c r="O28" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="29" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
@@ -4154,27 +4491,30 @@
       <c r="N29" s="1">
         <v>5</v>
       </c>
+      <c r="O29" s="1" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="F31" s="13" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="F31" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="I31" s="17" t="s">
+      <c r="G31" s="14"/>
+      <c r="I31" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="19"/>
-      <c r="N31" s="13" t="s">
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="17"/>
+      <c r="N31" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="O31" s="15"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
@@ -4478,25 +4818,25 @@
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="F45" s="12" t="s">
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="F45" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="M45" s="13" t="s">
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="M45" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="15"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="14"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
@@ -4950,23 +5290,23 @@
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="19"/>
-      <c r="H59" s="16" t="s">
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="17"/>
+      <c r="H59" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
@@ -5420,23 +5760,23 @@
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="J73" s="16" t="s">
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="J73" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="K73" s="16"/>
-      <c r="M73" s="16" t="s">
+      <c r="K73" s="18"/>
+      <c r="M73" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="N73" s="16"/>
+      <c r="N73" s="18"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B74" s="6" t="s">
@@ -5752,24 +6092,24 @@
       </c>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="19"/>
-      <c r="K87" s="12" t="s">
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="17"/>
+      <c r="K87" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="L87" s="12"/>
-      <c r="N87" s="13" t="s">
+      <c r="L87" s="19"/>
+      <c r="N87" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="O87" s="15"/>
+      <c r="O87" s="14"/>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="6" t="s">
@@ -5993,11 +6333,11 @@
       <c r="I94" s="7"/>
     </row>
     <row r="96" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C96" s="14"/>
-      <c r="D96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
@@ -6078,12 +6418,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="B18:O18"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="H59:O59"/>
     <mergeCell ref="B96:D96"/>
     <mergeCell ref="K87:L87"/>
-    <mergeCell ref="B18:N18"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="F45:K45"/>
@@ -6094,9 +6436,8 @@
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="N87:O87"/>
     <mergeCell ref="B73:H73"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="N31:O31"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1" xr:uid="{E72E32ED-3C6F-495C-9C6B-11494EBAFD4E}"/>
   </hyperlinks>
@@ -6106,22 +6447,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698E7371-5D81-4934-BBFC-EF6FE50D5163}">
-  <dimension ref="B2:S99"/>
+  <dimension ref="B2:T140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.28515625" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
@@ -6129,18 +6474,18 @@
         <v>180</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="H2" s="13" t="s">
+      <c r="F2" s="14"/>
+      <c r="H2" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="K2" s="13" t="s">
+      <c r="I2" s="14"/>
+      <c r="K2" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="L2" s="15"/>
+      <c r="L2" s="14"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -6221,20 +6566,20 @@
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="15"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -6655,21 +7000,21 @@
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="19"/>
-      <c r="K22" s="13" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+      <c r="K22" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="15"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="14"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
@@ -6937,22 +7282,22 @@
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="E36" s="16" t="s">
+      <c r="C36" s="14"/>
+      <c r="E36" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="F36" s="16"/>
-      <c r="H36" s="16" t="s">
+      <c r="F36" s="18"/>
+      <c r="H36" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="I36" s="16"/>
-      <c r="K36" s="13" t="s">
+      <c r="I36" s="18"/>
+      <c r="K36" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="L36" s="15"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
@@ -7095,21 +7440,21 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
@@ -7563,24 +7908,24 @@
       </c>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C60" s="14"/>
-      <c r="D60" s="15"/>
-      <c r="F60" s="17" t="s">
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="F60" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="19"/>
-      <c r="L60" s="13" t="s">
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="17"/>
+      <c r="L60" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="15"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="14"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
@@ -7965,26 +8310,26 @@
       </c>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="19"/>
-      <c r="G74" s="12" t="s">
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="17"/>
+      <c r="G74" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="H74" s="12"/>
-      <c r="J74" s="16" t="s">
+      <c r="H74" s="19"/>
+      <c r="J74" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="16"/>
-      <c r="O74" s="16"/>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="16"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="18"/>
+      <c r="Q74" s="18"/>
     </row>
     <row r="75" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
@@ -8429,28 +8774,28 @@
       </c>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="16"/>
-      <c r="J88" s="12" t="s">
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18"/>
+      <c r="J88" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="K88" s="12"/>
-      <c r="L88" s="12"/>
-      <c r="N88" s="12" t="s">
+      <c r="K88" s="19"/>
+      <c r="L88" s="19"/>
+      <c r="N88" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="O88" s="12"/>
-      <c r="P88" s="12"/>
-      <c r="Q88" s="12"/>
-      <c r="R88" s="12"/>
-      <c r="S88" s="12"/>
+      <c r="O88" s="19"/>
+      <c r="P88" s="19"/>
+      <c r="Q88" s="19"/>
+      <c r="R88" s="19"/>
+      <c r="S88" s="19"/>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="6" t="s">
@@ -8852,7 +9197,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" s="1">
         <v>8</v>
       </c>
@@ -8902,7 +9247,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" s="1">
         <v>9</v>
       </c>
@@ -8952,7 +9297,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" s="1">
         <v>10</v>
       </c>
@@ -9002,8 +9347,1237 @@
         <v>260</v>
       </c>
     </row>
+    <row r="102" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B102" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="F102" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+      <c r="K102" s="13"/>
+      <c r="L102" s="14"/>
+      <c r="N102" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="O102" s="19"/>
+      <c r="P102" s="19"/>
+      <c r="Q102" s="19"/>
+      <c r="R102" s="19"/>
+      <c r="S102" s="19"/>
+      <c r="T102" s="19"/>
+    </row>
+    <row r="103" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="P103" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="S103" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104" spans="2:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="1">
+        <v>1</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L104" s="4">
+        <v>45306</v>
+      </c>
+      <c r="N104" s="1">
+        <v>1</v>
+      </c>
+      <c r="O104" s="1">
+        <v>1</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q104" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="R104" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S104" s="4">
+        <v>45337</v>
+      </c>
+      <c r="T104" s="4">
+        <v>45398</v>
+      </c>
+    </row>
+    <row r="105" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B105" s="1">
+        <v>2</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D105" s="1">
+        <v>2</v>
+      </c>
+      <c r="F105" s="1">
+        <v>2</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L105" s="4">
+        <v>45311</v>
+      </c>
+      <c r="N105" s="1">
+        <v>2</v>
+      </c>
+      <c r="O105" s="1">
+        <v>2</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S105" s="4">
+        <v>45342</v>
+      </c>
+      <c r="T105" s="4">
+        <v>45399</v>
+      </c>
+    </row>
+    <row r="106" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B106" s="1">
+        <v>3</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D106" s="1">
+        <v>3</v>
+      </c>
+      <c r="F106" s="1">
+        <v>3</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L106" s="4">
+        <v>45323</v>
+      </c>
+      <c r="N106" s="1">
+        <v>3</v>
+      </c>
+      <c r="O106" s="1">
+        <v>3</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S106" s="4">
+        <v>45352</v>
+      </c>
+      <c r="T106" s="4">
+        <v>45400</v>
+      </c>
+    </row>
+    <row r="107" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B107" s="1">
+        <v>4</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1">
+        <v>4</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L107" s="4">
+        <v>45332</v>
+      </c>
+      <c r="N107" s="1">
+        <v>4</v>
+      </c>
+      <c r="O107" s="1">
+        <v>4</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q107" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S107" s="4">
+        <v>45361</v>
+      </c>
+      <c r="T107" s="4">
+        <v>45401</v>
+      </c>
+    </row>
+    <row r="108" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B108" s="1">
+        <v>5</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="F108" s="1">
+        <v>5</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L108" s="4">
+        <v>45337</v>
+      </c>
+      <c r="N108" s="1">
+        <v>5</v>
+      </c>
+      <c r="O108" s="1">
+        <v>5</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S108" s="4">
+        <v>45366</v>
+      </c>
+      <c r="T108" s="4">
+        <v>45402</v>
+      </c>
+    </row>
+    <row r="109" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B109" s="1">
+        <v>6</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D109" s="1">
+        <v>6</v>
+      </c>
+      <c r="F109" s="1">
+        <v>6</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L109" s="4">
+        <v>45342</v>
+      </c>
+      <c r="N109" s="1">
+        <v>6</v>
+      </c>
+      <c r="O109" s="1">
+        <v>6</v>
+      </c>
+      <c r="P109" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S109" s="4">
+        <v>45371</v>
+      </c>
+      <c r="T109" s="4">
+        <v>45403</v>
+      </c>
+    </row>
+    <row r="110" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B110" s="1">
+        <v>7</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D110" s="1">
+        <v>7</v>
+      </c>
+      <c r="F110" s="1">
+        <v>7</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L110" s="4">
+        <v>45352</v>
+      </c>
+      <c r="N110" s="1">
+        <v>7</v>
+      </c>
+      <c r="O110" s="1">
+        <v>7</v>
+      </c>
+      <c r="P110" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q110" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S110" s="4">
+        <v>45383</v>
+      </c>
+      <c r="T110" s="4">
+        <v>45404</v>
+      </c>
+    </row>
+    <row r="111" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B111" s="1">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D111" s="1">
+        <v>8</v>
+      </c>
+      <c r="F111" s="1">
+        <v>8</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L111" s="4">
+        <v>45356</v>
+      </c>
+      <c r="N111" s="1">
+        <v>8</v>
+      </c>
+      <c r="O111" s="1">
+        <v>8</v>
+      </c>
+      <c r="P111" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S111" s="4">
+        <v>45387</v>
+      </c>
+      <c r="T111" s="4">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="112" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B112" s="1">
+        <v>9</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D112" s="1">
+        <v>9</v>
+      </c>
+      <c r="F112" s="1">
+        <v>9</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L112" s="4">
+        <v>45361</v>
+      </c>
+      <c r="N112" s="1">
+        <v>9</v>
+      </c>
+      <c r="O112" s="1">
+        <v>9</v>
+      </c>
+      <c r="P112" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S112" s="4">
+        <v>45392</v>
+      </c>
+      <c r="T112" s="4">
+        <v>45406</v>
+      </c>
+    </row>
+    <row r="113" spans="2:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="L113" s="21"/>
+      <c r="N113" s="1">
+        <v>10</v>
+      </c>
+      <c r="O113" s="1">
+        <v>10</v>
+      </c>
+      <c r="P113" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="S113" s="4">
+        <v>45397</v>
+      </c>
+      <c r="T113" s="4">
+        <v>45407</v>
+      </c>
+    </row>
+    <row r="114" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S114" s="22"/>
+      <c r="T114" s="21"/>
+    </row>
+    <row r="115" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S115" s="22"/>
+      <c r="T115" s="21"/>
+    </row>
+    <row r="116" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B116" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="H116" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+      <c r="S116" s="22"/>
+      <c r="T116" s="22"/>
+    </row>
+    <row r="117" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B117" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B118" s="1">
+        <v>1</v>
+      </c>
+      <c r="C118" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F118" s="1">
+        <v>1</v>
+      </c>
+      <c r="H118" s="1">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="M118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B119" s="1">
+        <v>2</v>
+      </c>
+      <c r="C119" s="1">
+        <v>65000</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F119" s="1">
+        <v>2</v>
+      </c>
+      <c r="H119" s="1">
+        <v>2</v>
+      </c>
+      <c r="I119" s="1">
+        <v>65000</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="M119" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B120" s="1">
+        <v>3</v>
+      </c>
+      <c r="C120" s="1">
+        <v>55000</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F120" s="1">
+        <v>3</v>
+      </c>
+      <c r="H120" s="1">
+        <v>3</v>
+      </c>
+      <c r="I120" s="1">
+        <v>55000</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M120" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B121" s="1">
+        <v>4</v>
+      </c>
+      <c r="C121" s="1">
+        <v>70000</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F121" s="1">
+        <v>4</v>
+      </c>
+      <c r="H121" s="1">
+        <v>4</v>
+      </c>
+      <c r="I121" s="1">
+        <v>70000</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="M121" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B122" s="1">
+        <v>5</v>
+      </c>
+      <c r="C122" s="1">
+        <v>80000</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F122" s="1">
+        <v>5</v>
+      </c>
+      <c r="H122" s="1">
+        <v>5</v>
+      </c>
+      <c r="I122" s="1">
+        <v>80000</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M122" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B123" s="22"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+    </row>
+    <row r="125" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B125" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C125" s="13"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="14"/>
+      <c r="I125" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+      <c r="N125" s="1"/>
+    </row>
+    <row r="126" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="127" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B127" s="1">
+        <v>1</v>
+      </c>
+      <c r="C127" s="1">
+        <v>1</v>
+      </c>
+      <c r="D127" s="1">
+        <v>1</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1</v>
+      </c>
+      <c r="F127" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G127" s="1">
+        <v>50000</v>
+      </c>
+      <c r="I127" s="1">
+        <v>1</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+      <c r="K127" s="1">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1">
+        <v>1</v>
+      </c>
+      <c r="M127" s="1">
+        <v>1</v>
+      </c>
+      <c r="N127" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="128" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B128" s="1">
+        <v>2</v>
+      </c>
+      <c r="C128" s="1">
+        <v>2</v>
+      </c>
+      <c r="D128" s="1">
+        <v>2</v>
+      </c>
+      <c r="E128" s="1">
+        <v>1</v>
+      </c>
+      <c r="F128" s="1">
+        <v>65000</v>
+      </c>
+      <c r="G128" s="1">
+        <v>65000</v>
+      </c>
+      <c r="I128" s="1">
+        <v>2</v>
+      </c>
+      <c r="J128" s="1">
+        <v>2</v>
+      </c>
+      <c r="K128" s="1">
+        <v>2</v>
+      </c>
+      <c r="L128" s="1">
+        <v>2</v>
+      </c>
+      <c r="M128" s="1">
+        <v>1</v>
+      </c>
+      <c r="N128" s="1">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B129" s="1">
+        <v>3</v>
+      </c>
+      <c r="C129" s="1">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1">
+        <v>3</v>
+      </c>
+      <c r="E129" s="1">
+        <v>1</v>
+      </c>
+      <c r="F129" s="1">
+        <v>55000</v>
+      </c>
+      <c r="G129" s="1">
+        <v>55000</v>
+      </c>
+      <c r="I129" s="1">
+        <v>3</v>
+      </c>
+      <c r="J129" s="1">
+        <v>3</v>
+      </c>
+      <c r="K129" s="1">
+        <v>3</v>
+      </c>
+      <c r="L129" s="1">
+        <v>3</v>
+      </c>
+      <c r="M129" s="1">
+        <v>1</v>
+      </c>
+      <c r="N129" s="1">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B130" s="1">
+        <v>4</v>
+      </c>
+      <c r="C130" s="1">
+        <v>4</v>
+      </c>
+      <c r="D130" s="1">
+        <v>4</v>
+      </c>
+      <c r="E130" s="1">
+        <v>1</v>
+      </c>
+      <c r="F130" s="1">
+        <v>70000</v>
+      </c>
+      <c r="G130" s="1">
+        <v>70000</v>
+      </c>
+      <c r="I130" s="1">
+        <v>4</v>
+      </c>
+      <c r="J130" s="1">
+        <v>4</v>
+      </c>
+      <c r="K130" s="1">
+        <v>4</v>
+      </c>
+      <c r="L130" s="1">
+        <v>4</v>
+      </c>
+      <c r="M130" s="1">
+        <v>1</v>
+      </c>
+      <c r="N130" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B131" s="1">
+        <v>5</v>
+      </c>
+      <c r="C131" s="1">
+        <v>5</v>
+      </c>
+      <c r="D131" s="1">
+        <v>5</v>
+      </c>
+      <c r="E131" s="1">
+        <v>1</v>
+      </c>
+      <c r="F131" s="1">
+        <v>80000</v>
+      </c>
+      <c r="G131" s="1">
+        <v>80000</v>
+      </c>
+      <c r="I131" s="1">
+        <v>5</v>
+      </c>
+      <c r="J131" s="1">
+        <v>5</v>
+      </c>
+      <c r="K131" s="1">
+        <v>5</v>
+      </c>
+      <c r="L131" s="1">
+        <v>5</v>
+      </c>
+      <c r="M131" s="1">
+        <v>1</v>
+      </c>
+      <c r="N131" s="1">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="14"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="1">
+        <v>1</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F136" s="4">
+        <v>45306</v>
+      </c>
+      <c r="G136" s="4">
+        <v>45338</v>
+      </c>
+      <c r="H136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="1">
+        <v>2</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F137" s="4">
+        <v>45311</v>
+      </c>
+      <c r="G137" s="4">
+        <v>45339</v>
+      </c>
+      <c r="H137" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B138" s="1">
+        <v>3</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F138" s="4">
+        <v>45323</v>
+      </c>
+      <c r="G138" s="4">
+        <v>45340</v>
+      </c>
+      <c r="H138" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B139" s="1">
+        <v>4</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F139" s="4">
+        <v>45332</v>
+      </c>
+      <c r="G139" s="4">
+        <v>45341</v>
+      </c>
+      <c r="H139" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B140" s="1">
+        <v>5</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F140" s="4">
+        <v>45337</v>
+      </c>
+      <c r="G140" s="4">
+        <v>45342</v>
+      </c>
+      <c r="H140" s="1">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="25">
+    <mergeCell ref="B125:G125"/>
+    <mergeCell ref="B134:H134"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:L102"/>
+    <mergeCell ref="N102:T102"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="J74:Q74"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="N88:S88"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="F60:J60"/>
     <mergeCell ref="L60:O60"/>
@@ -9018,13 +10592,8 @@
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="B46:N46"/>
     <mergeCell ref="K36:L36"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="J74:Q74"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="N88:S88"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I10" r:id="rId1" xr:uid="{4C257B42-766D-4502-ACDF-D3F419CBACA6}"/>
   </hyperlinks>
